--- a/diseases/d122/2026-2029.xlsx
+++ b/diseases/d122/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -2294,9 +2288,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2687,9 +2678,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3675,9 +3663,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4068,9 +4053,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -5056,9 +5038,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5449,9 +5428,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6437,9 +6413,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="S35" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6830,9 +6803,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7966,9 +7936,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8362,9 +8329,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8510,9 +8474,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8658,9 +8619,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8806,9 +8764,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8954,9 +8909,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9350,9 +9302,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9498,9 +9447,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9646,9 +9592,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9792,9 +9735,6 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">

--- a/diseases/d122/2026-2029.xlsx
+++ b/diseases/d122/2026-2029.xlsx
@@ -7892,12 +7892,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7931,22 +7931,19 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -7971,7 +7968,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -7984,42 +7981,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8051,12 +8048,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -8090,29 +8087,29 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Trikinos</t>
+          <t>Trichinosis</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -8122,7 +8119,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -8137,7 +8134,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -8172,17 +8169,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>PHO IDTO current-year monthly preliminary trichinosis (trichinellosis) notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -8205,7 +8202,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_TRICHINELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -8218,42 +8215,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8282,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -8315,7 +8312,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -8337,68 +8334,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -8425,17 +8436,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8460,7 +8471,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -8474,76 +8485,165 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Trikinos</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8705,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -8750,7 +8850,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -8865,12 +8965,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8895,12 +8995,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8917,82 +9017,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -9019,17 +9105,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -9054,12 +9140,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -9068,165 +9154,76 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Trikinos</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN51" t="b">
-        <v>1</v>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9255,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -9288,7 +9285,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -9310,68 +9307,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9398,17 +9409,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -9433,7 +9444,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -9447,76 +9458,165 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Trikinos</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9678,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -9723,7 +9823,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -9805,6 +9905,296 @@
         </is>
       </c>
       <c r="BC55" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>trichinellosis</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -9926,7 +10316,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -9936,7 +10326,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -9956,7 +10346,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -9988,7 +10378,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d122/2026-2029.xlsx
+++ b/diseases/d122/2026-2029.xlsx
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1188,17 +1188,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1422,17 +1427,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -2703,7 +2713,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2711,17 +2721,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2937,7 +2952,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2945,17 +2960,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4078,7 +4098,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4086,17 +4106,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4312,7 +4337,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4320,17 +4345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -5453,7 +5483,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5461,17 +5491,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5687,7 +5722,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -5695,17 +5730,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6828,7 +6868,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -6836,17 +6876,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7062,7 +7107,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7070,17 +7115,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -8351,7 +8401,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8359,17 +8409,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8585,7 +8640,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8593,17 +8648,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9324,7 +9384,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -9332,17 +9392,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -9558,7 +9623,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -9566,17 +9631,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TRICHINELLOSIS</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
